--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAA13DD-6D98-4EF7-9540-9AEC98B1939B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417BAA1E-BD31-4FCF-8388-906EB2C8D39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5385" yWindow="780" windowWidth="22350" windowHeight="12870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -512,7 +512,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -521,7 +521,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417BAA1E-BD31-4FCF-8388-906EB2C8D39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867DECC5-9F69-4CAA-8BD2-7067132DF3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5385" yWindow="780" windowWidth="22350" windowHeight="12870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="1170" windowWidth="24285" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867DECC5-9F69-4CAA-8BD2-7067132DF3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAD1C6C-9B62-47E7-8088-AFF88E25B128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1170" windowWidth="24285" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4935" yWindow="1320" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -932,7 +932,7 @@
         <v>22</v>
       </c>
       <c r="D7" s="4">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4">
         <v>20</v>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAD1C6C-9B62-47E7-8088-AFF88E25B128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7578C05-3B2D-41FC-8B6F-22486667F414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4935" yWindow="1320" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7890" yWindow="1395" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</t>
   </si>
@@ -163,6 +163,46 @@
   </si>
   <si>
     <t>float[]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_shark_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>상어</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>상어다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Shark</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DObject/Monster_Shark</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Slime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DObject/Monster_Slime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_slime_1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1000,15 +1040,33 @@
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7">
+        <v>50</v>
+      </c>
+      <c r="E9" s="7">
+        <v>30</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>45</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -1021,15 +1079,33 @@
       <c r="S9" s="5"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="A10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1">
+        <v>100</v>
+      </c>
+      <c r="E10" s="1">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>49</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7578C05-3B2D-41FC-8B6F-22486667F414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753FE343-C0BD-443A-8DDF-EBA328D8C53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7890" yWindow="1395" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="885" windowWidth="22035" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -972,7 +972,7 @@
         <v>22</v>
       </c>
       <c r="D7" s="4">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E7" s="4">
         <v>20</v>
@@ -1050,7 +1050,7 @@
         <v>43</v>
       </c>
       <c r="D9" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E9" s="7">
         <v>30</v>
